--- a/03_Cluster_groups/Proteome/01_Cluster/c_data/01_cluster.xlsx
+++ b/03_Cluster_groups/Proteome/01_Cluster/c_data/01_cluster.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="230">
   <si>
     <t>sheet</t>
   </si>
@@ -517,6 +517,12 @@
     <t>1.0.5</t>
   </si>
   <si>
+    <t>limma</t>
+  </si>
+  <si>
+    <t>3.68.1</t>
+  </si>
+  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -659,6 +665,12 @@
   </si>
   <si>
     <t>1.4.6.1</t>
+  </si>
+  <si>
+    <t>statmod</t>
+  </si>
+  <si>
+    <t>1.5.1</t>
   </si>
   <si>
     <t>tibble</t>
@@ -3694,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -4112,7 +4124,7 @@
         <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -4145,7 +4157,7 @@
         <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -4156,7 +4168,7 @@
         <v>174</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -4288,7 +4300,7 @@
         <v>198</v>
       </c>
       <c r="C54" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -4299,7 +4311,7 @@
         <v>200</v>
       </c>
       <c r="C55" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -4321,7 +4333,7 @@
         <v>204</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -4332,7 +4344,7 @@
         <v>206</v>
       </c>
       <c r="C58" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -4395,7 +4407,7 @@
         <v>217</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="C64" t="s">
         <v>97</v>
@@ -4403,10 +4415,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C65" t="s">
         <v>97</v>
@@ -4414,10 +4426,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
-        <v>221</v>
+        <v>129</v>
       </c>
       <c r="C66" t="s">
         <v>97</v>
@@ -4442,6 +4454,28 @@
         <v>225</v>
       </c>
       <c r="C68" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>228</v>
+      </c>
+      <c r="B70" t="s">
+        <v>229</v>
+      </c>
+      <c r="C70" t="s">
         <v>97</v>
       </c>
     </row>
